--- a/PROPOSITIONS.xlsx
+++ b/PROPOSITIONS.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J260"/>
+  <dimension ref="A1:L260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -435,6 +435,8 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +490,16 @@
           <t>Ton commentaire</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>PRE-TRI CLAUDE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Raison (Claude)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -495,7 +507,6 @@
           <t>Les Produits Laitiers</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>haute</t>
@@ -524,6 +535,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -564,6 +585,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -604,6 +635,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -644,6 +685,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -651,7 +702,6 @@
           <t>Leporc</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>basse</t>
@@ -680,6 +730,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -687,7 +747,6 @@
           <t>Interview Métiers</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>haute</t>
@@ -716,6 +775,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -723,7 +792,6 @@
           <t>Mister V</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>haute</t>
@@ -752,6 +820,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -792,6 +870,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -832,6 +920,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -872,6 +970,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -879,7 +987,6 @@
           <t>Histoire Métiers</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>haute</t>
@@ -908,6 +1015,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -915,7 +1032,6 @@
           <t>Nos Chefs nous manquent</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>haute</t>
@@ -944,6 +1060,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -984,6 +1110,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -991,7 +1127,6 @@
           <t>MIV 2021</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1020,6 +1155,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1060,6 +1205,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1100,6 +1255,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1140,6 +1305,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1180,6 +1355,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1220,6 +1405,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1227,7 +1422,6 @@
           <t>Made in viande 2014</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1256,6 +1450,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1296,6 +1500,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1303,7 +1517,6 @@
           <t>Le Monde</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1332,6 +1545,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1339,7 +1562,6 @@
           <t>Thomas</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>basse</t>
@@ -1368,6 +1590,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1408,6 +1640,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1415,7 +1657,6 @@
           <t>Milk Check</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1444,6 +1685,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1451,7 +1702,6 @@
           <t>Et si on en parlait</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1480,6 +1730,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1520,6 +1780,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1527,7 +1797,6 @@
           <t>Nos amis pour la vie</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1556,6 +1825,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1563,7 +1842,6 @@
           <t>Chorégraphie</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>basse</t>
@@ -1592,6 +1870,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1599,7 +1887,6 @@
           <t>La Sauce de la Paix</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1628,6 +1915,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1635,7 +1932,6 @@
           <t>Génération XYZ</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1664,6 +1960,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1671,7 +1977,6 @@
           <t>Brigitte Lecordier</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1700,6 +2005,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1707,7 +2022,6 @@
           <t>Check</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>basse</t>
@@ -1736,6 +2050,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1743,7 +2067,6 @@
           <t>Pascal</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>basse</t>
@@ -1772,6 +2095,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1812,6 +2145,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1852,6 +2195,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1859,7 +2212,6 @@
           <t>Pub TV</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1888,6 +2240,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1895,7 +2257,6 @@
           <t>Grand Voyage</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1924,6 +2285,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1931,7 +2302,6 @@
           <t>Pures sensations</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>haute</t>
@@ -1960,6 +2330,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1967,7 +2347,6 @@
           <t>Interview</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>basse</t>
@@ -1996,6 +2375,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2003,7 +2392,6 @@
           <t>On the road to Foie Gras</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2032,6 +2420,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2039,7 +2437,6 @@
           <t>Nathalie de Masterchef Nathal</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2068,6 +2465,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2075,7 +2482,6 @@
           <t>La Brigade</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2099,6 +2505,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2134,6 +2550,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2141,7 +2567,6 @@
           <t>Morgan VS</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2170,6 +2595,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2177,7 +2612,6 @@
           <t>Tour de France</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2206,6 +2640,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2213,7 +2657,6 @@
           <t>Bertrand</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>basse</t>
@@ -2242,6 +2685,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2282,6 +2735,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2289,7 +2752,6 @@
           <t>DANS NOS ASSIETTES</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2318,6 +2780,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2325,7 +2797,6 @@
           <t>Nouvelle pub</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2354,6 +2825,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2361,7 +2842,6 @@
           <t>Le lait c'est gai</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2390,6 +2870,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2430,6 +2920,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2465,6 +2965,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2505,6 +3015,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2512,7 +3032,6 @@
           <t>MADE in VIANDE 2017</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2541,6 +3060,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2581,6 +3110,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2588,7 +3127,6 @@
           <t>Traçabilité</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>basse</t>
@@ -2617,6 +3155,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2624,7 +3172,6 @@
           <t>Recette Cuisine Viande</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2653,6 +3200,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2660,7 +3217,6 @@
           <t>Recette de Cuisine Viande</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2689,6 +3245,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2696,7 +3262,6 @@
           <t>Stéphanie Sardain et Vincent</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2725,6 +3290,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2732,7 +3307,6 @@
           <t>Spot radio</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2761,6 +3335,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2801,6 +3385,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2841,6 +3435,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2881,6 +3485,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2888,7 +3502,6 @@
           <t>Pierre Chomet Foie Gras poêlé</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2917,6 +3530,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2924,7 +3547,6 @@
           <t>Pierre Chomet Un foie gras cr</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>haute</t>
@@ -2953,6 +3575,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2960,7 +3592,6 @@
           <t>Nicolas</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>basse</t>
@@ -2989,6 +3620,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2996,7 +3637,6 @@
           <t>XYZ Generation</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3025,6 +3665,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3032,7 +3682,6 @@
           <t>Matthias Marc et Pierre Chome</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3061,6 +3710,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3068,7 +3727,6 @@
           <t>Foie Gras in pictures</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3097,6 +3755,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3137,6 +3805,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3144,7 +3822,6 @@
           <t>Jean Sorhouet</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3173,6 +3850,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3180,7 +3867,6 @@
           <t>Concours</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3209,6 +3895,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3249,6 +3945,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3284,6 +3990,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3291,7 +4007,6 @@
           <t>Vincent</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3313,6 +4028,16 @@
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3322,7 +4047,6 @@
           <t>Freddy Gladieux</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3344,6 +4068,16 @@
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -3353,7 +4087,6 @@
           <t>Laura</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3375,6 +4108,16 @@
       <c r="G79" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3384,7 +4127,6 @@
           <t>Denitsa</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3406,6 +4148,16 @@
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3415,7 +4167,6 @@
           <t>Benjamin</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3437,6 +4188,16 @@
       <c r="G81" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3446,7 +4207,6 @@
           <t>Morgan</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3468,6 +4228,16 @@
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3477,7 +4247,6 @@
           <t>David</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3499,6 +4268,16 @@
       <c r="G83" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3536,6 +4315,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3543,7 +4332,6 @@
           <t>Julia</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3565,6 +4353,16 @@
       <c r="G85" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3574,7 +4372,6 @@
           <t>Emile</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3596,6 +4393,16 @@
       <c r="G86" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3605,7 +4412,6 @@
           <t>Marty</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3627,6 +4433,16 @@
       <c r="G87" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3636,7 +4452,6 @@
           <t>Isabelle</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3658,6 +4473,16 @@
       <c r="G88" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3667,7 +4492,6 @@
           <t>mathilde</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
           <t>basse</t>
@@ -3689,6 +4513,16 @@
       <c r="G89" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -3698,7 +4532,6 @@
           <t>Théo Juice</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3720,6 +4553,16 @@
       <c r="G90" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -3757,6 +4600,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3792,6 +4645,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3799,7 +4662,6 @@
           <t>Salon International de l'Agriculture</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3821,6 +4683,16 @@
       <c r="G93" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
         </is>
       </c>
     </row>
@@ -3858,6 +4730,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3865,7 +4747,6 @@
           <t>Laura Martinez</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3887,6 +4768,16 @@
       <c r="G95" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -3896,7 +4787,6 @@
           <t>Fabien Patanchon</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3918,6 +4808,16 @@
       <c r="G96" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -3927,7 +4827,6 @@
           <t>Label Rouge</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3949,6 +4848,16 @@
       <c r="G97" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -3958,7 +4867,6 @@
           <t>Les produits tripiers</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
           <t>haute</t>
@@ -3980,6 +4888,16 @@
       <c r="G98" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -3989,7 +4907,6 @@
           <t>Marine</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
           <t>basse</t>
@@ -4011,6 +4928,16 @@
       <c r="G99" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4947,6 @@
           <t>Fabrice</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
           <t>basse</t>
@@ -4042,6 +4968,16 @@
       <c r="G100" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -4079,6 +5015,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4086,7 +5032,6 @@
           <t>Chef Pâtissier</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4108,6 +5053,16 @@
       <c r="G102" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -4117,7 +5072,6 @@
           <t>Philippine Jaillet</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4139,6 +5093,16 @@
       <c r="G103" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>suivre ce compte (chef - categorie separee)</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>chef ou patissier : ta regle les traite a part</t>
         </is>
       </c>
     </row>
@@ -4148,7 +5112,6 @@
           <t>Guillaume Sanchez</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4170,6 +5133,16 @@
       <c r="G104" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>suivre ce compte (chef - categorie separee)</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>chef ou patissier : ta regle les traite a part</t>
         </is>
       </c>
     </row>
@@ -4179,7 +5152,6 @@
           <t>Jorick Dorignac</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4201,6 +5173,16 @@
       <c r="G105" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>suivre ce compte (chef - categorie separee)</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>chef ou patissier : ta regle les traite a part</t>
         </is>
       </c>
     </row>
@@ -4210,7 +5192,6 @@
           <t>Quentin Mauro</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4232,6 +5213,16 @@
       <c r="G106" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -4269,6 +5260,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4276,7 +5277,6 @@
           <t>Mehdi Maïzi et avec la partic</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4298,6 +5298,16 @@
       <c r="G108" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -4335,6 +5345,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4342,7 +5362,6 @@
           <t>LES JONES</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4364,6 +5383,16 @@
       <c r="G110" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -4373,7 +5402,6 @@
           <t>Jamy</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
           <t>basse</t>
@@ -4395,6 +5423,16 @@
       <c r="G111" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -4404,7 +5442,6 @@
           <t>Hakim Jemili</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4426,6 +5463,16 @@
       <c r="G112" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -4463,6 +5510,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4470,7 +5527,6 @@
           <t>Jamy Du lait</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4492,6 +5548,16 @@
       <c r="G114" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -4529,6 +5595,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4564,6 +5640,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>suivre ce compte (chef - categorie separee)</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>chef ou patissier : ta regle les traite a part</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4571,7 +5657,6 @@
           <t>Sido Cuisto</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4593,6 +5678,16 @@
       <c r="G117" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -4602,7 +5697,6 @@
           <t>Fromage Tu penses que tu ne p</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4624,6 +5718,16 @@
       <c r="G118" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -4633,7 +5737,6 @@
           <t>Mister V diffusé le vendredi</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4655,6 +5758,16 @@
       <c r="G119" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -4664,7 +5777,6 @@
           <t>MISTER V Redécouvrez la pub T</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4686,6 +5798,16 @@
       <c r="G120" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -4695,7 +5817,6 @@
           <t>Mister V Vous nous l'aviez de</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4717,6 +5838,16 @@
       <c r="G121" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -4754,6 +5885,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4761,7 +5902,6 @@
           <t>Pâtes Tu penses que tu ne peu</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4783,6 +5923,16 @@
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -4792,7 +5942,6 @@
           <t>Eric Birlouez</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4814,6 +5963,16 @@
       <c r="G124" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -4823,7 +5982,6 @@
           <t>Florent De Maria</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4845,6 +6003,16 @@
       <c r="G125" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -4854,7 +6022,6 @@
           <t>Pub Fromage</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4876,6 +6043,16 @@
       <c r="G126" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -4885,7 +6062,6 @@
           <t>Fromage - Le Monstre</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4907,6 +6083,16 @@
       <c r="G127" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -4916,7 +6102,6 @@
           <t>Régénérez votre corps</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4938,6 +6123,16 @@
       <c r="G128" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -4947,7 +6142,6 @@
           <t>Fromages de France</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
           <t>haute</t>
@@ -4969,6 +6163,16 @@
       <c r="G129" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -4978,7 +6182,6 @@
           <t>L'emmental et les pâtes</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5000,6 +6203,16 @@
       <c r="G130" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -5009,7 +6222,6 @@
           <t>Paf paf paf le loup</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5031,6 +6243,16 @@
       <c r="G131" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -5040,7 +6262,6 @@
           <t>Loïc ce qui fait</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5062,6 +6283,16 @@
       <c r="G132" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5071,7 +6302,6 @@
           <t>L’Amour Bœuf - Épisode 07</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5093,6 +6323,16 @@
       <c r="G133" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5130,6 +6370,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5137,7 +6387,6 @@
           <t>L'Amour Bœuf - Épisode 06</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5159,6 +6408,16 @@
       <c r="G135" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5168,7 +6427,6 @@
           <t>L'Amour Bœuf - Épisode 05</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5190,6 +6448,16 @@
       <c r="G136" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5199,7 +6467,6 @@
           <t>L’Amour Bœuf - Épisode 04</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5221,6 +6488,16 @@
       <c r="G137" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5230,7 +6507,6 @@
           <t>L'Amour Bœuf - Épisode 03</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5252,6 +6528,16 @@
       <c r="G138" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5261,7 +6547,6 @@
           <t>L'Amour Bœuf - Épisode 02</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5283,6 +6568,16 @@
       <c r="G139" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5292,7 +6587,6 @@
           <t>L'Amour Bœuf - Épisode 01</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5314,6 +6608,16 @@
       <c r="G140" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5323,7 +6627,6 @@
           <t>Amour Bœuf</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5345,6 +6648,16 @@
       <c r="G141" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -5382,6 +6695,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5389,7 +6712,6 @@
           <t>Jean-Louis PEYRAUD Un monde s</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5411,6 +6733,16 @@
       <c r="G143" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5420,7 +6752,6 @@
           <t>Philippe SELLIER L’herbe</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5442,6 +6773,16 @@
       <c r="G144" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -5451,7 +6792,6 @@
           <t>Maryvonne LAGARONNE En France</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5473,6 +6813,16 @@
       <c r="G145" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5482,7 +6832,6 @@
           <t>Marine VAN SIMMERTIER En Fran</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5504,6 +6853,16 @@
       <c r="G146" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5513,7 +6872,6 @@
           <t>Sébastien VALTEAU L’élevage a</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5535,6 +6893,16 @@
       <c r="G147" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5572,6 +6940,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5579,7 +6957,6 @@
           <t>Viande Bio</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5601,6 +6978,16 @@
       <c r="G149" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -5610,7 +6997,6 @@
           <t>Les aventures de Quentin</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5632,6 +7018,16 @@
       <c r="G150" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -5641,7 +7037,6 @@
           <t>Alisson Apprentie Boucher</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5663,6 +7058,16 @@
       <c r="G151" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -5672,7 +7077,6 @@
           <t>Comptine 04</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5694,6 +7098,16 @@
       <c r="G152" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5703,7 +7117,6 @@
           <t>Comptine 03</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5725,6 +7138,16 @@
       <c r="G153" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5734,7 +7157,6 @@
           <t>Comptine 02</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5756,6 +7178,16 @@
       <c r="G154" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5765,7 +7197,6 @@
           <t>Comptine 01</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5787,6 +7218,16 @@
       <c r="G155" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5796,7 +7237,6 @@
           <t>Claude Petitguyot 01</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5818,6 +7258,16 @@
       <c r="G156" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5827,7 +7277,6 @@
           <t>Claude Petitguyot 02</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5849,6 +7298,16 @@
       <c r="G157" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5858,7 +7317,6 @@
           <t>Claude Petitguyot 03</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5880,6 +7338,16 @@
       <c r="G158" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5889,7 +7357,6 @@
           <t>Claude Petitguyot 04</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5911,6 +7378,16 @@
       <c r="G159" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5920,7 +7397,6 @@
           <t>Hervé Pillaud A l'occasion de</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5942,6 +7418,16 @@
       <c r="G160" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -5951,7 +7437,6 @@
           <t>Charline Picon - Championne d</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
           <t>haute</t>
@@ -5973,6 +7458,16 @@
       <c r="G161" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -6010,6 +7505,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6017,7 +7522,6 @@
           <t>Trailer</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
           <t>basse</t>
@@ -6039,6 +7543,16 @@
       <c r="G163" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -6048,7 +7562,6 @@
           <t>Changement climatique</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6070,6 +7583,16 @@
       <c r="G164" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -6079,7 +7602,6 @@
           <t>Salma du blog Cuisinons en co</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6101,6 +7623,16 @@
       <c r="G165" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -6110,7 +7642,6 @@
           <t>Tiphaine du blog Gourmandiser</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6132,6 +7663,16 @@
       <c r="G166" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -6169,6 +7710,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6176,7 +7727,6 @@
           <t>Anne du blog Panier de Saison</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6198,6 +7748,16 @@
       <c r="G168" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -6235,6 +7795,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6270,6 +7840,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6277,7 +7857,6 @@
           <t>Edda du blog Un déjeuner de S</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6299,6 +7878,16 @@
       <c r="G171" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -6308,7 +7897,6 @@
           <t>Dorian du blog Mais Pourquoi</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6330,6 +7918,16 @@
       <c r="G172" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -6339,7 +7937,6 @@
           <t>Nadia du blog Paprikas</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6361,6 +7958,16 @@
       <c r="G173" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -6370,7 +7977,6 @@
           <t>Interview de Yoni Saada</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6392,6 +7998,16 @@
       <c r="G174" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>suivre ce compte (chef - categorie separee)</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>chef ou patissier : ta regle les traite a part</t>
         </is>
       </c>
     </row>
@@ -6401,7 +8017,6 @@
           <t>Véronique</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
           <t>basse</t>
@@ -6423,6 +8038,16 @@
       <c r="G175" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -6432,7 +8057,6 @@
           <t>Lionel</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
           <t>basse</t>
@@ -6454,6 +8078,16 @@
       <c r="G176" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -6463,7 +8097,6 @@
           <t>Nicolas Dupont-Aignan</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6485,6 +8118,16 @@
       <c r="G177" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>ignorer (politique)</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>personnalite politique en visite : hors registre createurs</t>
         </is>
       </c>
     </row>
@@ -6494,7 +8137,6 @@
           <t>Hervé Morin</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6516,6 +8158,16 @@
       <c r="G178" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>ignorer (politique)</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>personnalite politique en visite : hors registre createurs</t>
         </is>
       </c>
     </row>
@@ -6525,7 +8177,6 @@
           <t>François Fillon</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6547,6 +8198,16 @@
       <c r="G179" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>ignorer (politique)</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>personnalite politique en visite : hors registre createurs</t>
         </is>
       </c>
     </row>
@@ -6556,7 +8217,6 @@
           <t>Harlem Désir</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6578,6 +8238,16 @@
       <c r="G180" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>ignorer (politique)</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>personnalite politique en visite : hors registre createurs</t>
         </is>
       </c>
     </row>
@@ -6587,7 +8257,6 @@
           <t>Guillaume Garot</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6609,6 +8278,16 @@
       <c r="G181" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>ignorer (politique)</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>personnalite politique en visite : hors registre createurs</t>
         </is>
       </c>
     </row>
@@ -6618,7 +8297,6 @@
           <t>Eric Andrieu</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6640,6 +8318,16 @@
       <c r="G182" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>ignorer (politique)</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>personnalite politique en visite : hors registre createurs</t>
         </is>
       </c>
     </row>
@@ -6649,7 +8337,6 @@
           <t>Bruno Le Maire</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6671,6 +8358,16 @@
       <c r="G183" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>ignorer (politique)</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>personnalite politique en visite : hors registre createurs</t>
         </is>
       </c>
     </row>
@@ -6680,7 +8377,6 @@
           <t>Antoine Herth</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6702,6 +8398,16 @@
       <c r="G184" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>ignorer (politique)</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>personnalite politique en visite : hors registre createurs</t>
         </is>
       </c>
     </row>
@@ -6711,7 +8417,6 @@
           <t>La ferme du futur</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6733,6 +8438,16 @@
       <c r="G185" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -6742,7 +8457,6 @@
           <t>Découpe de tête de veau</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6764,6 +8478,16 @@
       <c r="G186" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -6773,7 +8497,6 @@
           <t>La chasse aux insectes</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6795,6 +8518,16 @@
       <c r="G187" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -6804,7 +8537,6 @@
           <t>Safari à la ferme</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6826,6 +8558,16 @@
       <c r="G188" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -6835,7 +8577,6 @@
           <t>Frédéric</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
           <t>basse</t>
@@ -6857,6 +8598,16 @@
       <c r="G189" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -6866,7 +8617,6 @@
           <t>I L'OVIN</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6888,6 +8638,16 @@
       <c r="G190" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -6897,7 +8657,6 @@
           <t>L'amour est dans le pré</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
           <t>haute</t>
@@ -6919,6 +8678,16 @@
       <c r="G191" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
         </is>
       </c>
     </row>
@@ -6928,7 +8697,6 @@
           <t>Guillaume</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
         <is>
           <t>basse</t>
@@ -6950,6 +8718,16 @@
       <c r="G192" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -6959,7 +8737,6 @@
           <t>Fabien</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
         <is>
           <t>basse</t>
@@ -6981,6 +8758,16 @@
       <c r="G193" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -6990,7 +8777,6 @@
           <t>Jean-Benoît</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
         <is>
           <t>basse</t>
@@ -7012,6 +8798,16 @@
       <c r="G194" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -7021,7 +8817,6 @@
           <t>Jean-Paul</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
           <t>basse</t>
@@ -7043,6 +8838,16 @@
       <c r="G195" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -7052,7 +8857,6 @@
           <t>Olivier</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
           <t>basse</t>
@@ -7074,6 +8878,16 @@
       <c r="G196" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -7083,7 +8897,6 @@
           <t>Xavier</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
         <is>
           <t>basse</t>
@@ -7105,6 +8918,16 @@
       <c r="G197" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -7142,6 +8965,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7149,7 +8982,6 @@
           <t>Filière viande</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7171,6 +9003,16 @@
       <c r="G199" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -7180,7 +9022,6 @@
           <t>Expert d'élevage</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7202,6 +9043,16 @@
       <c r="G200" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -7211,7 +9062,6 @@
           <t>Viande Elevage Bio</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7233,6 +9083,16 @@
       <c r="G201" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -7242,7 +9102,6 @@
           <t>Joy Sorman</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7264,6 +9123,16 @@
       <c r="G202" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -7301,6 +9170,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7308,7 +9187,6 @@
           <t>Vincent Simon</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7330,6 +9208,16 @@
       <c r="G204" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -7339,7 +9227,6 @@
           <t>Boris Tillot</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7361,6 +9248,16 @@
       <c r="G205" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -7370,7 +9267,6 @@
           <t>Vincent Simon Partez à la ren</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7392,6 +9288,16 @@
       <c r="G206" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -7401,7 +9307,6 @@
           <t>Boris Tillot Partez à la renc</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7423,6 +9328,16 @@
       <c r="G207" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -7432,7 +9347,6 @@
           <t>Frédéric Boulajeri</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7454,6 +9368,16 @@
       <c r="G208" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -7463,7 +9387,6 @@
           <t>Emmanuel Coyaud</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7485,6 +9408,16 @@
       <c r="G209" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -7494,7 +9427,6 @@
           <t>Geoffroy Terrasson</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7516,6 +9448,16 @@
       <c r="G210" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -7525,7 +9467,6 @@
           <t>Frédéric Boulajeri Partez à l</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7547,6 +9488,16 @@
       <c r="G211" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -7556,7 +9507,6 @@
           <t>Emmanuel Coyaud Partez à la r</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7578,6 +9528,16 @@
       <c r="G212" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -7587,7 +9547,6 @@
           <t>Geoffroy Terrasson Partez à l</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7609,6 +9568,16 @@
       <c r="G213" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -7618,7 +9587,6 @@
           <t>Steeve Bellanger</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7640,6 +9608,16 @@
       <c r="G214" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -7649,7 +9627,6 @@
           <t>Vincent Kerdoncuff</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7671,6 +9648,16 @@
       <c r="G215" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -7680,7 +9667,6 @@
           <t>Steeve Bellanger Partez à la</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7702,6 +9688,16 @@
       <c r="G216" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -7711,7 +9707,6 @@
           <t>Gino Catena Partez à la renco</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7733,6 +9728,16 @@
       <c r="G217" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -7742,7 +9747,6 @@
           <t>Vincent Kerdoncuff Partez à l</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7764,6 +9768,16 @@
       <c r="G218" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -7773,7 +9787,6 @@
           <t>Yves Puget</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7795,6 +9808,16 @@
       <c r="G219" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -7804,7 +9827,6 @@
           <t>Pierre Chomet et Marie</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7826,6 +9848,16 @@
       <c r="G220" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -7835,7 +9867,6 @@
           <t>Pierre Chomet Foie Gras au to</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7857,6 +9888,16 @@
       <c r="G221" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -7866,7 +9907,6 @@
           <t>Pierre Chomet Pain toasté</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7888,6 +9928,16 @@
       <c r="G222" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -7897,7 +9947,6 @@
           <t>Foie Gras in Reels</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7919,6 +9968,16 @@
       <c r="G223" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -7928,7 +9987,6 @@
           <t>Foie Gras in Reels - E2</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7950,6 +10008,16 @@
       <c r="G224" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -7959,7 +10027,6 @@
           <t>Foie Gras in Reels - E1</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
           <t>haute</t>
@@ -7981,6 +10048,16 @@
       <c r="G225" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -7990,7 +10067,6 @@
           <t>Le Foie Gras en Reels-E2</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8012,6 +10088,16 @@
       <c r="G226" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -8021,7 +10107,6 @@
           <t>Florian et tenter de le surpr</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8043,6 +10128,16 @@
       <c r="G227" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -8080,6 +10175,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8087,7 +10192,6 @@
           <t>Florian Boucherie</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8109,6 +10213,16 @@
       <c r="G229" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -8118,7 +10232,6 @@
           <t>Fabien Chevalier</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
       <c r="C230" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8140,6 +10253,16 @@
       <c r="G230" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -8149,7 +10272,6 @@
           <t>Sylvie qui élève des canards</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8171,6 +10293,16 @@
       <c r="G231" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -8180,7 +10312,6 @@
           <t>Philippe Geneletti</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8202,6 +10333,16 @@
       <c r="G232" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -8211,7 +10352,6 @@
           <t>WEB SÉRIE CULINAIRE</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8233,6 +10373,16 @@
       <c r="G233" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -8242,7 +10392,6 @@
           <t>Michel Fruchet</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8264,6 +10413,16 @@
       <c r="G234" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -8273,7 +10432,6 @@
           <t>Le Magret</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8295,6 +10453,16 @@
       <c r="G235" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -8304,7 +10472,6 @@
           <t>Evénement</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
         <is>
           <t>basse</t>
@@ -8326,6 +10493,16 @@
       <c r="G236" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -8335,7 +10512,6 @@
           <t>Secret de Cheffe en vidéo</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8357,6 +10533,16 @@
       <c r="G237" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -8366,7 +10552,6 @@
           <t>Challenge Foie Gras 2014</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8388,6 +10573,16 @@
       <c r="G238" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -8397,7 +10592,6 @@
           <t>André Daguin</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8419,6 +10613,16 @@
       <c r="G239" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -8428,7 +10632,6 @@
           <t>Jean-Claude Narcy De</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8450,6 +10653,16 @@
       <c r="G240" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -8459,7 +10672,6 @@
           <t>Foie Gras 2017</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8481,6 +10693,16 @@
       <c r="G241" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -8490,7 +10712,6 @@
           <t>Clotilde Jacoulot Découvrez l</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8512,6 +10733,16 @@
       <c r="G242" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -8521,7 +10752,6 @@
           <t>Frédéric Jaunault Frédéric Ja</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8543,6 +10773,16 @@
       <c r="G243" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -8552,7 +10792,6 @@
           <t>En vidéo</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8574,6 +10813,16 @@
       <c r="G244" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -8583,7 +10832,6 @@
           <t>Foie Gras</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8605,6 +10853,16 @@
       <c r="G245" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -8614,7 +10872,6 @@
           <t>Foie Gras et Magret</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8636,6 +10893,16 @@
       <c r="G246" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -8645,7 +10912,6 @@
           <t>Geneviève Bellet</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8667,6 +10933,16 @@
       <c r="G247" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -8676,7 +10952,6 @@
           <t>Oies et Canards</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8698,6 +10973,16 @@
       <c r="G248" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>
@@ -8707,7 +10992,6 @@
           <t>Nathalie de Masterchef</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8729,6 +11013,16 @@
       <c r="G249" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
         </is>
       </c>
     </row>
@@ -8738,7 +11032,6 @@
           <t>Air France Découvrez l'élevag</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8760,6 +11053,16 @@
       <c r="G250" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
         </is>
       </c>
     </row>
@@ -8769,7 +11072,6 @@
           <t>Michel Idiart</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8791,6 +11093,16 @@
       <c r="G251" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -8800,7 +11112,6 @@
           <t>Pascal Nowak</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8822,6 +11133,16 @@
       <c r="G252" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -8831,7 +11152,6 @@
           <t>Jean-François Aucouturier</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8853,6 +11173,16 @@
       <c r="G253" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>ignorer (professionnel de la filiere)</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>eleveur, boucher, expert interviewe : pas un createur</t>
         </is>
       </c>
     </row>
@@ -8890,6 +11220,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>ignorer (institution/evenement/commerce)</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>pas un createur</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8897,7 +11237,6 @@
           <t>Dorian</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
         <is>
           <t>basse</t>
@@ -8919,6 +11258,16 @@
       <c r="G255" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -8928,7 +11277,6 @@
           <t>Audrey</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
         <is>
           <t>basse</t>
@@ -8950,6 +11298,16 @@
       <c r="G256" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>ignorer (trop generique)</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>prenom ou mot seul, personne d'identifiable</t>
         </is>
       </c>
     </row>
@@ -8959,7 +11317,6 @@
           <t>Julien Duboué Régalez-vous pe</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr">
         <is>
           <t>haute</t>
@@ -8981,6 +11338,16 @@
       <c r="G257" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>ignorer (fragment de titre)</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>morceau de titre, pas une entite — le nom propre existe ailleurs dans la liste</t>
         </is>
       </c>
     </row>
@@ -9018,6 +11385,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>suivre ce compte (createur)</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>createur ou personnalite de contenu, identifiable</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9025,7 +11402,6 @@
           <t>Pad Thaï</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr">
         <is>
           <t>haute</t>
@@ -9047,6 +11423,16 @@
       <c r="G259" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>a toi de voir</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>je n'arrive pas a trancher sur les preuves disponibles</t>
         </is>
       </c>
     </row>
@@ -9082,6 +11468,16 @@
       <c r="G260" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>signal pour le dictionnaire</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>serie, campagne ou compte du lobby lui-meme</t>
         </is>
       </c>
     </row>

--- a/PROPOSITIONS.xlsx
+++ b/PROPOSITIONS.xlsx
@@ -535,6 +535,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -585,6 +595,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -635,6 +655,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -685,6 +715,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -730,6 +770,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -775,6 +825,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -820,6 +880,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -920,6 +990,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -970,6 +1050,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -1015,6 +1105,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -1060,6 +1160,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -1110,6 +1220,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -1155,6 +1275,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -1205,6 +1335,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -1255,6 +1395,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -1305,6 +1455,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -1355,6 +1515,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -1405,6 +1575,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -1450,6 +1630,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -1500,6 +1690,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -1545,6 +1745,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -1590,6 +1800,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -1640,6 +1860,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -1685,6 +1915,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -1730,6 +1970,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -1780,6 +2030,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -1825,6 +2085,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -1870,6 +2140,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -1915,6 +2195,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -1960,6 +2250,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -2005,6 +2305,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -2050,6 +2360,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -2095,6 +2415,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -2145,6 +2475,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -2195,6 +2535,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -2285,6 +2635,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -2330,6 +2690,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -2375,6 +2745,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -2420,6 +2800,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -2465,6 +2855,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -2505,6 +2905,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -2550,6 +2960,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -2595,6 +3015,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -2640,6 +3070,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -2685,6 +3125,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -2735,6 +3185,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -2780,6 +3240,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -2870,6 +3340,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -2920,6 +3400,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -2965,6 +3455,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -3015,6 +3515,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -3060,6 +3570,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -3155,6 +3675,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -3200,6 +3730,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -3245,6 +3785,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -3290,6 +3840,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -3385,6 +3945,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -3435,6 +4005,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -3485,6 +4065,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -3530,6 +4120,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -3575,6 +4175,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -3620,6 +4230,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -3665,6 +4285,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -3710,6 +4340,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -3755,6 +4395,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -3805,6 +4455,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -3850,6 +4510,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -3895,6 +4565,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -3945,6 +4625,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -3990,6 +4680,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -4030,6 +4730,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4070,6 +4780,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -4110,6 +4830,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4150,6 +4880,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4190,6 +4930,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4230,6 +4980,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4270,6 +5030,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4315,6 +5085,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -4355,6 +5135,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4395,6 +5185,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4435,6 +5235,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4475,6 +5285,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4515,6 +5335,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4555,6 +5385,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -4600,6 +5440,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -4645,6 +5495,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -4685,6 +5545,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -4770,6 +5640,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -4810,6 +5690,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -4850,6 +5740,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -4890,6 +5790,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -4930,6 +5840,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -4970,6 +5890,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -5095,6 +6025,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>suivre ce compte (chef - categorie separee)</t>
@@ -5135,6 +6075,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>suivre ce compte (chef - categorie separee)</t>
@@ -5175,6 +6125,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>suivre ce compte (chef - categorie separee)</t>
@@ -5215,6 +6175,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -5260,6 +6230,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -5300,6 +6280,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -5345,6 +6335,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -5425,6 +6425,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -5465,6 +6475,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -5510,6 +6530,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -5550,6 +6580,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K114" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -5640,6 +6680,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr">
         <is>
           <t>suivre ce compte (chef - categorie separee)</t>
@@ -5680,6 +6730,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -5720,6 +6780,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K118" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -5760,6 +6830,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K119" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -5800,6 +6880,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -5840,6 +6930,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -5885,6 +6985,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -5925,6 +7035,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -5965,6 +7085,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -6005,6 +7135,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K125" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -6165,6 +7305,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K129" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -6285,6 +7435,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K132" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6325,6 +7485,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6370,6 +7540,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -6410,6 +7590,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6450,6 +7640,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6490,6 +7690,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K137" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6530,6 +7740,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6570,6 +7790,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6610,6 +7840,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6695,6 +7935,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -6735,6 +7985,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K143" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6815,6 +8075,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6855,6 +8125,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6895,6 +8175,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -6940,6 +8230,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -6980,6 +8280,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -7060,6 +8370,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -7100,6 +8420,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -7140,6 +8470,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -7180,6 +8520,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -7220,6 +8570,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -7260,6 +8620,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -7300,6 +8670,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -7340,6 +8720,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -7380,6 +8770,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -7420,6 +8820,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -7460,6 +8870,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -7505,6 +8925,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -7545,6 +8975,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K163" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -7625,6 +9065,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -7665,6 +9115,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -7710,6 +9170,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K167" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -7750,6 +9220,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -7795,6 +9275,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -7840,6 +9330,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K170" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -7880,6 +9380,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K171" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -7920,6 +9430,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -7960,6 +9480,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K173" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -8000,6 +9530,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr">
         <is>
           <t>suivre ce compte (chef - categorie separee)</t>
@@ -8040,6 +9580,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K175" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -8080,6 +9630,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K176" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -8120,6 +9680,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K177" t="inlineStr">
         <is>
           <t>ignorer (politique)</t>
@@ -8160,6 +9730,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr">
         <is>
           <t>ignorer (politique)</t>
@@ -8200,6 +9780,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K179" t="inlineStr">
         <is>
           <t>ignorer (politique)</t>
@@ -8240,6 +9830,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr">
         <is>
           <t>ignorer (politique)</t>
@@ -8280,6 +9880,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K181" t="inlineStr">
         <is>
           <t>ignorer (politique)</t>
@@ -8320,6 +9930,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K182" t="inlineStr">
         <is>
           <t>ignorer (politique)</t>
@@ -8360,6 +9980,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
           <t>ignorer (politique)</t>
@@ -8400,6 +10030,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr">
         <is>
           <t>ignorer (politique)</t>
@@ -8600,6 +10240,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -8640,6 +10290,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -8680,6 +10340,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -8720,6 +10390,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K192" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -8760,6 +10440,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -8800,6 +10490,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -8840,6 +10540,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K195" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -8880,6 +10590,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K196" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -8920,6 +10640,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K197" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -8965,6 +10695,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K198" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -9005,6 +10745,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K199" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -9045,6 +10795,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K200" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -9085,6 +10845,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K201" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -9125,6 +10895,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K202" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -9170,6 +10950,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K203" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -9210,6 +11000,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K204" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -9250,6 +11050,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K205" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -9290,6 +11100,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K206" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -9330,6 +11150,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K207" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -9370,6 +11200,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K208" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -9410,6 +11250,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K209" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -9450,6 +11300,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K210" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -9490,6 +11350,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K211" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -9530,6 +11400,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K212" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -9570,6 +11450,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K213" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -9610,6 +11500,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K214" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -9650,6 +11550,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K215" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -9690,6 +11600,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K216" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -9730,6 +11650,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K217" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -9770,6 +11700,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K218" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -9810,6 +11750,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K219" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -9890,6 +11840,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K221" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -9970,6 +11930,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K223" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10010,6 +11980,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K224" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10050,6 +12030,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K225" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10090,6 +12080,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K226" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10130,6 +12130,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K227" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -10175,6 +12185,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K228" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -10255,6 +12275,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K230" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -10295,6 +12325,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K231" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -10335,6 +12375,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K232" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -10375,6 +12425,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K233" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10415,6 +12475,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K234" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -10455,6 +12525,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K235" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10495,6 +12575,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K236" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -10535,6 +12625,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K237" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10575,6 +12675,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K238" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10615,6 +12725,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K239" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -10695,6 +12815,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K241" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10735,6 +12865,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K242" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -10775,6 +12915,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K243" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -10855,6 +13005,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K245" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10895,6 +13055,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K246" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -10935,6 +13105,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K247" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -10975,6 +13155,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K248" t="inlineStr">
         <is>
           <t>signal pour le dictionnaire</t>
@@ -11015,6 +13205,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K249" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -11055,6 +13255,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K250" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -11095,6 +13305,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K251" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -11135,6 +13355,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K252" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -11175,6 +13405,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K253" t="inlineStr">
         <is>
           <t>ignorer (professionnel de la filiere)</t>
@@ -11220,6 +13460,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K254" t="inlineStr">
         <is>
           <t>ignorer (institution/evenement/commerce)</t>
@@ -11260,6 +13510,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K255" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -11300,6 +13560,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K256" t="inlineStr">
         <is>
           <t>ignorer (trop generique)</t>
@@ -11340,6 +13610,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>ignorer</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K257" t="inlineStr">
         <is>
           <t>ignorer (fragment de titre)</t>
@@ -11385,6 +13665,16 @@
           <t>ouvrir</t>
         </is>
       </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>suivre ce compte</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
+        </is>
+      </c>
       <c r="K258" t="inlineStr">
         <is>
           <t>suivre ce compte (createur)</t>
@@ -11468,6 +13758,16 @@
       <c r="G260" s="2" t="inlineStr">
         <is>
           <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>je ne sais pas</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>valide en bloc par Vincent (06/09)</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
